--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-antecedent-familial-observe.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-antecedent-familial-observe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-antecedent-familial-observe.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-antecedent-familial-observe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$107</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="344">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -574,6 +574,132 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -584,15 +710,140 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+    <t>Description narrative de la valeur de l'observation</t>
+  </si>
+  <si>
+    <t>Observation.text.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.text.compression</t>
+  </si>
+  <si>
+    <t>Compression</t>
+  </si>
+  <si>
+    <t>Indicates whether the raw byte data is compressed, and what compression algorithm was used.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDACompressionAlgorithm</t>
+  </si>
+  <si>
+    <t>ED.compression</t>
+  </si>
+  <si>
+    <t>Observation.text.integrityCheck</t>
+  </si>
+  <si>
+    <t>Integrity Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary {http://hl7.org/cda/stds/core/StructureDefinition/bin}
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Description narrative de la valeur de l'observation
-* text.reference 1..1 MS
+    <t>The integrity check is a short binary value representing a cryptographically strong checksum that is calculated over the binary data. The purpose of this property, when communicated with a reference is for anyone to validate later whether the reference still resolved to the same data that the reference resolved to when the encapsulated data value with reference was created.</t>
+  </si>
+  <si>
+    <t>ED.integrityCheck</t>
+  </si>
+  <si>
+    <t>Observation.text.integrityCheckAlgorithm</t>
+  </si>
+  <si>
+    <t>Integrity Check Algorithm</t>
+  </si>
+  <si>
+    <t>Specifies the algorithm used to compute the integrityCheck value. The cryptographically strong checksum algorithm Secure Hash Algorithm-1 (SHA-1) is currently the industry standard. It has superseded the MD5 algorithm only a couple of years ago, when certain flaws in the security of MD5 were discovered. Currently the SHA-1 hash algorithm is the default choice for the integrity check algorithm. Note that SHA-256 is also entering widespread usage.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-IntegrityCheckAlgorithm|2.0.0</t>
+  </si>
+  <si>
+    <t>ED.integrityCheckAlgorithm</t>
+  </si>
+  <si>
+    <t>Observation.text.language</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>For character based information the language property specifies the human language of the text.</t>
+  </si>
+  <si>
+    <t>ED.language</t>
+  </si>
+  <si>
+    <t>Observation.text.mediaType</t>
+  </si>
+  <si>
+    <t>Media Type</t>
+  </si>
+  <si>
+    <t>Identifies the type of the encapsulated data and identifies a method to interpret or render the data.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-MediaType</t>
+  </si>
+  <si>
+    <t>ED.mediaType</t>
+  </si>
+  <si>
+    <t>Observation.text.representation</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/BinaryDataEncoding</t>
+  </si>
+  <si>
+    <t>ED.representation</t>
+  </si>
+  <si>
+    <t>Observation.text.xmlText</t>
+  </si>
+  <si>
+    <t>Allows for mixed text content. If @representation='B64', this SHALL be a base64binary string.</t>
+  </si>
+  <si>
+    <t>Data that is primarily intended for human interpretation or for further machine processing is outside the scope of HL7. This includes unformatted or formatted written language, multimedia data, or structured information as defined by a different standard (e.g., XML-signatures.)</t>
+  </si>
+  <si>
+    <t>This element is represented in XML as textual content. The actual name "xmlText" will not appear in a CDA instance.</t>
+  </si>
+  <si>
+    <t>ED.xmlText</t>
+  </si>
+  <si>
+    <t>Observation.text.reference</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/TEL
 </t>
   </si>
   <si>
+    <t>A telecommunication address (TEL), such as a URL for HTTP or FTP, which will resolve to precisely the same binary data that could as well have been provided as inline data.</t>
+  </si>
+  <si>
+    <t>ED.reference</t>
+  </si>
+  <si>
+    <t>Observation.text.thumbnail</t>
+  </si>
+  <si>
+    <t>Thumbnail</t>
+  </si>
+  <si>
+    <t>An abbreviated rendition of the full data. A thumbnail requires significantly fewer resources than the full data, while still maintaining some distinctive similarity with the full data. A thumbnail is typically used with by-reference encapsulated data. It allows a user to select data more efficiently before actually downloading through the reference.</t>
+  </si>
+  <si>
+    <t>ED.thumbnail</t>
+  </si>
+  <si>
     <t>Observation.statusCode</t>
   </si>
   <si>
@@ -608,123 +859,34 @@
     <t>Observation.statusCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
     <t>completed</t>
   </si>
   <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.statusCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
-  </si>
-  <si>
     <t>Observation.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.effectiveTime</t>
@@ -742,9 +904,6 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
 </t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
@@ -1238,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK86"/>
+  <dimension ref="A1:AK107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.015625" customWidth="true" bestFit="true"/>
@@ -5175,7 +5334,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>175</v>
       </c>
@@ -5194,7 +5353,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5489,7 +5648,9 @@
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5506,10 +5667,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5535,13 +5698,11 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5559,7 +5720,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5579,16 +5740,18 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>75</v>
       </c>
@@ -5605,12 +5768,12 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="M43" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5660,7 +5823,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5680,16 +5843,18 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>75</v>
       </c>
@@ -5706,11 +5871,9 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
         <v>188</v>
       </c>
@@ -5739,29 +5902,31 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5791,7 +5956,7 @@
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5809,11 +5974,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5840,11 +6005,13 @@
         <v>74</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>74</v>
@@ -5862,7 +6029,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5882,17 +6049,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
@@ -5910,11 +6077,11 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5926,7 +6093,7 @@
         <v>74</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>74</v>
@@ -5965,7 +6132,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5983,28 +6150,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6013,11 +6180,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6068,7 +6235,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6088,23 +6255,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -6116,11 +6281,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6171,7 +6336,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6191,23 +6356,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -6223,7 +6386,7 @@
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6274,7 +6437,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6294,23 +6457,23 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6322,11 +6485,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6377,7 +6540,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6397,21 +6560,23 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6423,11 +6588,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6478,13 +6643,13 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>74</v>
@@ -6498,21 +6663,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6524,11 +6691,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6579,13 +6746,13 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6599,23 +6766,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -6627,12 +6792,10 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="L53" s="2"/>
-      <c r="M53" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6682,7 +6845,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6700,28 +6863,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E54" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -6730,12 +6891,12 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="L54" s="2"/>
-      <c r="M54" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6785,13 +6946,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -6815,13 +6976,13 @@
         <v>74</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>228</v>
+        <v>84</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -6833,11 +6994,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>229</v>
+        <v>86</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6864,13 +7025,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -6888,13 +7047,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>230</v>
+        <v>89</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -6906,18 +7065,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E56" s="2"/>
+      <c r="E56" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
@@ -6925,7 +7086,7 @@
         <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>74</v>
@@ -6934,13 +7095,11 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6967,13 +7126,11 @@
         <v>74</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>74</v>
+        <v>231</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>74</v>
@@ -6991,7 +7148,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7011,16 +7168,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
@@ -7040,7 +7199,9 @@
         <v>235</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+      <c r="M57" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7066,29 +7227,31 @@
         <v>74</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7117,7 +7280,9 @@
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
@@ -7134,10 +7299,12 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>239</v>
+        <v>85</v>
       </c>
       <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
+      <c r="M58" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7163,13 +7330,11 @@
         <v>74</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7187,7 +7352,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7207,16 +7372,18 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
@@ -7233,10 +7400,12 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
+      <c r="M59" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7262,11 +7431,13 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>241</v>
+        <v>74</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7284,7 +7455,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7304,21 +7475,23 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
@@ -7330,10 +7503,12 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>243</v>
+        <v>85</v>
       </c>
       <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
+      <c r="M60" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7359,13 +7534,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7383,13 +7556,13 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>74</v>
@@ -7401,12 +7574,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7420,7 +7593,7 @@
         <v>75</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>74</v>
@@ -7429,14 +7602,10 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7466,7 +7635,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7484,13 +7653,13 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>74</v>
@@ -7502,12 +7671,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7521,7 +7690,7 @@
         <v>75</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>74</v>
@@ -7530,15 +7699,17 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>235</v>
+        <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>74</v>
@@ -7563,11 +7734,13 @@
         <v>74</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>249</v>
+        <v>74</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -7585,13 +7758,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>74</v>
@@ -7603,26 +7776,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>74</v>
@@ -7631,13 +7806,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7688,13 +7861,13 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>74</v>
@@ -7708,16 +7881,18 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
@@ -7734,10 +7909,12 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
+      <c r="M64" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -7787,7 +7964,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7805,12 +7982,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7818,13 +7995,13 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -7833,10 +8010,14 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -7862,13 +8043,11 @@
         <v>74</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -7886,13 +8065,13 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>74</v>
@@ -7906,21 +8085,23 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E66" s="2"/>
+      <c r="E66" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -7932,10 +8113,12 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>257</v>
+        <v>85</v>
       </c>
       <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
+      <c r="M66" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -7961,13 +8144,11 @@
         <v>74</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -7985,13 +8166,13 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>256</v>
+        <v>89</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>74</v>
@@ -8005,16 +8186,18 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
@@ -8031,10 +8214,12 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
+      <c r="M67" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8045,7 +8230,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>74</v>
+        <v>275</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8084,13 +8269,13 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>258</v>
+        <v>185</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>74</v>
@@ -8104,21 +8289,23 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -8130,10 +8317,12 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>261</v>
+        <v>112</v>
       </c>
       <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
+      <c r="M68" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8183,13 +8372,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>74</v>
@@ -8203,21 +8392,23 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8229,10 +8420,12 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
+      <c r="M69" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8282,13 +8475,13 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>74</v>
@@ -8302,21 +8495,23 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -8328,10 +8523,12 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>265</v>
+        <v>102</v>
       </c>
       <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
+      <c r="M70" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8381,13 +8578,13 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>264</v>
+        <v>197</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>74</v>
@@ -8401,21 +8598,23 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" s="2"/>
+      <c r="E71" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>74</v>
@@ -8427,10 +8626,12 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>267</v>
+        <v>102</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+      <c r="M71" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8480,13 +8681,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>266</v>
+        <v>201</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8500,10 +8701,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8514,7 +8715,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8526,10 +8727,12 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>269</v>
+        <v>203</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
+      <c r="M72" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8579,13 +8782,13 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>74</v>
@@ -8599,10 +8802,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8613,7 +8816,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>74</v>
@@ -8625,10 +8828,12 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>271</v>
+        <v>102</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
+      <c r="M73" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -8678,13 +8883,13 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>270</v>
+        <v>208</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>74</v>
@@ -8698,21 +8903,23 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>74</v>
@@ -8724,11 +8931,11 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8779,13 +8986,13 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>272</v>
+        <v>213</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>74</v>
@@ -8799,23 +9006,23 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -8827,11 +9034,11 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -8858,11 +9065,13 @@
         <v>74</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>74</v>
@@ -8880,13 +9089,13 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>89</v>
+        <v>218</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>74</v>
@@ -8900,21 +9109,23 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>74</v>
@@ -8926,11 +9137,11 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -8981,7 +9192,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -8999,12 +9210,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9018,7 +9229,7 @@
         <v>75</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>74</v>
@@ -9027,11 +9238,13 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L77" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="M77" t="s" s="2">
-        <v>96</v>
+        <v>287</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9082,7 +9295,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9094,7 +9307,7 @@
         <v>74</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>74</v>
@@ -9102,18 +9315,16 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E78" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
@@ -9130,12 +9341,10 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>85</v>
+        <v>289</v>
       </c>
       <c r="L78" s="2"/>
-      <c r="M78" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9161,11 +9370,11 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>87</v>
+        <v>250</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>88</v>
+        <v>290</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9183,7 +9392,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>89</v>
+        <v>288</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9203,18 +9412,16 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
@@ -9231,12 +9438,10 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>102</v>
+        <v>292</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9286,7 +9491,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>104</v>
+        <v>291</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9306,18 +9511,16 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
@@ -9334,12 +9537,10 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9365,13 +9566,11 @@
         <v>74</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>74</v>
+        <v>294</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>74</v>
@@ -9389,7 +9588,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>109</v>
+        <v>293</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9409,23 +9608,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E81" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>74</v>
@@ -9437,12 +9634,10 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>112</v>
+        <v>296</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9450,7 +9645,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>74</v>
@@ -9492,13 +9687,13 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>74</v>
@@ -9510,28 +9705,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E82" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>74</v>
@@ -9540,11 +9733,13 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L82" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="M82" t="s" s="2">
-        <v>118</v>
+        <v>298</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9571,13 +9766,11 @@
         <v>74</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>74</v>
+        <v>299</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -9595,13 +9788,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>119</v>
+        <v>297</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -9613,12 +9806,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9629,10 +9822,10 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>74</v>
@@ -9641,11 +9834,13 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L83" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="M83" t="s" s="2">
-        <v>122</v>
+        <v>301</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9672,13 +9867,11 @@
         <v>74</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>74</v>
+        <v>302</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>74</v>
@@ -9696,7 +9889,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9716,10 +9909,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9742,10 +9935,14 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -9753,7 +9950,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>74</v>
@@ -9771,11 +9968,13 @@
         <v>74</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -9793,13 +9992,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -9813,10 +10012,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9824,7 +10023,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>75</v>
@@ -9839,7 +10038,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -9892,10 +10091,10 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>75</v>
@@ -9912,10 +10111,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -9938,7 +10137,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -9991,7 +10190,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10009,8 +10208,2113 @@
         <v>74</v>
       </c>
     </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y96" s="2"/>
+      <c r="Z96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L97" s="2"/>
+      <c r="M97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L98" s="2"/>
+      <c r="M98" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y99" s="2"/>
+      <c r="Z99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L100" s="2"/>
+      <c r="M100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E101" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L104" s="2"/>
+      <c r="M104" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y105" s="2"/>
+      <c r="Z105" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2"/>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2"/>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK86">
+  <autoFilter ref="A1:AK107">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10020,7 +12324,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI85">
+  <conditionalFormatting sqref="A2:AI106">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-antecedent-familial-observe.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-antecedent-familial-observe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6165,7 +6165,7 @@
         <v>199</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>75</v>
